--- a/risk/financiero/seed/estados_financieros_tabla.xlsx
+++ b/risk/financiero/seed/estados_financieros_tabla.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-16T19:21:53</t>
+          <t>2026-10-15T14:12:53</t>
         </is>
       </c>
     </row>
